--- a/planilha de controle de estoque.xlsx
+++ b/planilha de controle de estoque.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Odirlei Guilherme\Desktop\controle_de_estoque_basico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C57ED36-687F-4B74-95E0-01E5F134A0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11A3E976-6574-4C9F-9A17-EC0406ED2E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20280" yWindow="-135" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{FB90DC12-CE7E-421E-A7F9-F06FD8601840}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
   <si>
     <t>Produto</t>
   </si>
@@ -200,7 +200,20 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -228,12 +241,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}" name="Tabela5" displayName="Tabela5" ref="B2:E24" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B2:E24" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}" name="Tabela5" displayName="Tabela5" ref="B2:E27" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B2:E27" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9A824ECF-4997-4FB3-8467-CA5F746211D1}" name="Data" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{6F519A01-4485-4303-A5F9-1109AE4DC2DA}" name="Produto" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{F0E480FA-F451-40F8-AC3B-1DC003CAD38F}" name="Status " dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9A824ECF-4997-4FB3-8467-CA5F746211D1}" name="Data" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{6F519A01-4485-4303-A5F9-1109AE4DC2DA}" name="Produto" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F0E480FA-F451-40F8-AC3B-1DC003CAD38F}" name="Status " dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{853DA4E0-565B-4E84-ACE2-FAB8B85CA4C3}" name="Quantidade"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -537,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137AD64A-E144-47FE-A0E9-95F7C892ACF1}">
-  <dimension ref="B2:F24"/>
+  <dimension ref="B2:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -858,7 +871,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
-        <v>46023</v>
+        <v>46327</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>18</v>
@@ -869,6 +882,39 @@
       <c r="E24" s="2">
         <v>12</v>
       </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>46327</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="4">
+        <v>46327</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1030,15 +1076,15 @@
       </c>
       <c r="D9" s="7">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B9)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>Ok</v>
+        <v>Comprar</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -1118,15 +1164,15 @@
       </c>
       <c r="D13" s="7">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B13)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F13" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>Ok</v>
+        <v>Comprar</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -1241,6 +1287,11 @@
       <c r="H18" s="7"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B4:F18">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$F4="Comprar"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/planilha de controle de estoque.xlsx
+++ b/planilha de controle de estoque.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Odirlei Guilherme\Desktop\controle_de_estoque_basico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11A3E976-6574-4C9F-9A17-EC0406ED2E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C310F1FA-6519-41F5-A9F6-FD1A8813AAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20280" yWindow="-135" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{FB90DC12-CE7E-421E-A7F9-F06FD8601840}"/>
   </bookViews>
   <sheets>
     <sheet name="Entrada e Saída" sheetId="1" r:id="rId1"/>
     <sheet name="Saldo" sheetId="2" r:id="rId2"/>
+    <sheet name="Menu" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="27">
   <si>
     <t>Produto</t>
   </si>
@@ -101,13 +102,19 @@
   </si>
   <si>
     <t>Mínimo</t>
+  </si>
+  <si>
+    <t>Controle de Estoque</t>
+  </si>
+  <si>
+    <t>Entada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,8 +136,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00FF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,6 +163,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF08DE69"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -171,11 +224,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -188,14 +238,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -203,7 +266,7 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
@@ -215,6 +278,9 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -224,11 +290,14 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00FF00"/>
+      <color rgb="FF08DE69"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -240,13 +309,376 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Retângulo: Cantos Arredondados 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E16FB62C-8CB8-4CE0-B4A5-04FDA0CF21D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3762375" y="161925"/>
+          <a:ext cx="1743075" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>Menu </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" baseline="0"/>
+            <a:t>Principal</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>578427</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>128155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>492702</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>413905</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Retângulo: Cantos Arredondados 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE48053-2900-4D27-80E6-9FCE5E7E196A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3461904" y="128155"/>
+          <a:ext cx="1732684" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>Menu Principal</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Retângulo: Cantos Arredondados 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71F571D3-3CD8-71EA-93A9-E74AD0201B0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="342900" y="1295400"/>
+          <a:ext cx="2876550" cy="704850"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="2400"/>
+            <a:t>Entrada e Saída</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Retângulo: Cantos Arredondados 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21D00603-2359-4280-A95F-C80C5182EC8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="352425" y="2190750"/>
+          <a:ext cx="2876550" cy="704850"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="2400"/>
+            <a:t>Saldo</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>457200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Retângulo: Cantos Arredondados 4">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C71C9374-5998-4520-A4E4-3EBDFE388166}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3752850" y="171450"/>
+          <a:ext cx="1743075" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0"/>
+            <a:t>Menu </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>Principal</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}" name="Tabela5" displayName="Tabela5" ref="B2:E27" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B2:E27" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}" name="Tabela5" displayName="Tabela5" ref="B3:E30" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B3:E30" xr:uid="{36F923C0-43EC-4309-9C6B-28398D46868F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9A824ECF-4997-4FB3-8467-CA5F746211D1}" name="Data" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{6F519A01-4485-4303-A5F9-1109AE4DC2DA}" name="Produto" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{F0E480FA-F451-40F8-AC3B-1DC003CAD38F}" name="Status " dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{9A824ECF-4997-4FB3-8467-CA5F746211D1}" name="Data" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{6F519A01-4485-4303-A5F9-1109AE4DC2DA}" name="Produto" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F0E480FA-F451-40F8-AC3B-1DC003CAD38F}" name="Status " dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{853DA4E0-565B-4E84-ACE2-FAB8B85CA4C3}" name="Quantidade"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -550,221 +982,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137AD64A-E144-47FE-A0E9-95F7C892ACF1}">
-  <dimension ref="B2:F27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+    <row r="1" spans="1:5" s="13" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" s="15" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
         <v>46315</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3">
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
         <v>46315</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
         <v>46315</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
         <v>46317</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6">
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
         <v>46318</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7">
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
         <v>46318</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8">
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
         <v>46318</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9">
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
         <v>46318</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10">
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
         <v>46318</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11">
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
         <v>46321</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12">
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
         <v>46323</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
-        <v>46323</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E14">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="3">
         <v>46323</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="3">
+        <v>46323</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="4">
-        <v>46323</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E16">
@@ -772,13 +1196,13 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>46323</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E17">
@@ -786,505 +1210,554 @@
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="4">
+      <c r="B18" s="3">
+        <v>46323</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="3">
         <v>46324</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="4">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="3">
         <v>46324</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="3">
         <v>46324</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E21" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="4">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="3">
         <v>46325</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="3">
+        <v>46325</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="4">
-        <v>46325</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="E23" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="3">
+        <v>46327</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="4">
+      <c r="E28" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
         <v>46327</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E29" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="4">
-        <v>46327</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="4">
-        <v>46327</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="4">
-        <v>46327</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="2"/>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3C6A7C-358A-4193-853C-B78C12F1FBEE}">
-  <dimension ref="B3:I18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+    <row r="1" spans="1:9" s="13" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="12"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B4)</f>
         <v>15</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B4)</f>
         <v>3</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <f>C4-D4</f>
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="str">
+      <c r="F4" s="9" t="str">
         <f>IF(E4&lt;C4*$I$3,"Comprar","Ok")</f>
         <v>Ok</v>
       </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B5)</f>
         <v>25</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B5)</f>
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
         <f t="shared" ref="E5:E18" si="0">C5-D5</f>
-        <v>21</v>
-      </c>
-      <c r="F5" s="7" t="str">
+        <v>25</v>
+      </c>
+      <c r="F5" s="9" t="str">
         <f t="shared" ref="F5:F18" si="1">IF(E5&lt;C5*$I$3,"Comprar","Ok")</f>
         <v>Ok</v>
       </c>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B6)</f>
         <v>50</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B6)</f>
-        <v>10</v>
-      </c>
-      <c r="E6" s="7">
+        <v>47</v>
+      </c>
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="F6" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Comprar</v>
+      </c>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B7)</f>
+        <v>25</v>
+      </c>
+      <c r="D7" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B7)</f>
+        <v>21</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Comprar</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B8)</f>
+        <v>60</v>
+      </c>
+      <c r="D8" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="F8" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Ok</v>
       </c>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B7)</f>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B9)</f>
+        <v>43</v>
+      </c>
+      <c r="D9" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B9)</f>
+        <v>12</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="F9" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ok</v>
+      </c>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B10)</f>
+        <v>30</v>
+      </c>
+      <c r="D10" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F10" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ok</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B11)</f>
+        <v>50</v>
+      </c>
+      <c r="D11" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B11)</f>
+        <v>2</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="F11" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ok</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B12)</f>
+        <v>20</v>
+      </c>
+      <c r="D12" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B12)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F12" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ok</v>
+      </c>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B13)</f>
         <v>25</v>
       </c>
-      <c r="D7" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B7)</f>
+      <c r="D13" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B13)</f>
+        <v>21</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F13" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Comprar</v>
+      </c>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B14)</f>
+        <v>30</v>
+      </c>
+      <c r="D14" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B14)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E14" s="9">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F14" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ok</v>
+      </c>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B15)</f>
+        <v>30</v>
+      </c>
+      <c r="D15" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B15)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F15" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Ok</v>
+      </c>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B16)</f>
+        <v>25</v>
+      </c>
+      <c r="D16" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B16)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F16" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Ok</v>
       </c>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B8)</f>
-        <v>60</v>
-      </c>
-      <c r="D8" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B8)</f>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B17)</f>
+        <v>25</v>
+      </c>
+      <c r="D17" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B17)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="str">
+        <v>25</v>
+      </c>
+      <c r="F17" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Ok</v>
       </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B9)</f>
-        <v>15</v>
-      </c>
-      <c r="D9" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B9)</f>
-        <v>14</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B18)</f>
+        <v>25</v>
+      </c>
+      <c r="D18" s="9">
+        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B18)</f>
+        <v>21</v>
+      </c>
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="str">
+        <v>4</v>
+      </c>
+      <c r="F18" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Comprar</v>
       </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B10)</f>
-        <v>30</v>
-      </c>
-      <c r="D10" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B10)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="F10" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B11)</f>
-        <v>50</v>
-      </c>
-      <c r="D11" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B11)</f>
-        <v>2</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="F11" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B12)</f>
-        <v>20</v>
-      </c>
-      <c r="D12" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B12)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="F12" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B13)</f>
-        <v>25</v>
-      </c>
-      <c r="D13" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B13)</f>
-        <v>21</v>
-      </c>
-      <c r="E13" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F13" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Comprar</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B14)</f>
-        <v>30</v>
-      </c>
-      <c r="D14" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B14)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="F14" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B15)</f>
-        <v>30</v>
-      </c>
-      <c r="D15" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B15)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="7">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="F15" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B16)</f>
-        <v>25</v>
-      </c>
-      <c r="D16" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B16)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="F16" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B17)</f>
-        <v>25</v>
-      </c>
-      <c r="D17" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B17)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="F17" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Ok</v>
-      </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$C$3,'Entrada e Saída'!C:C,Saldo!$B18)</f>
-        <v>25</v>
-      </c>
-      <c r="D18" s="7">
-        <f>SUMIFS('Entrada e Saída'!E:E,'Entrada e Saída'!D:D,Saldo!$D$3,'Entrada e Saída'!C:C,Saldo!$B18)</f>
-        <v>21</v>
-      </c>
-      <c r="E18" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F18" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>Comprar</v>
-      </c>
-      <c r="H18" s="7"/>
+      <c r="H18" s="6"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:F18">
@@ -1293,5 +1766,27 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B08E067-B59C-4FE8-8914-C0AFF7B203DE}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="13" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" s="14" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/planilha de controle de estoque.xlsx
+++ b/planilha de controle de estoque.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Odirlei Guilherme\Desktop\controle_de_estoque_basico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C310F1FA-6519-41F5-A9F6-FD1A8813AAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD26C3DD-4E75-48E9-BC7E-91689E48033A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20280" yWindow="-135" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{FB90DC12-CE7E-421E-A7F9-F06FD8601840}"/>
+    <workbookView xWindow="20280" yWindow="-135" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{FB90DC12-CE7E-421E-A7F9-F06FD8601840}"/>
   </bookViews>
   <sheets>
     <sheet name="Entrada e Saída" sheetId="1" r:id="rId1"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="B1" s="12"/>
     </row>
-    <row r="2" spans="1:5" s="15" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:5" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>3</v>

--- a/planilha de controle de estoque.xlsx
+++ b/planilha de controle de estoque.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Odirlei Guilherme\Desktop\controle_de_estoque_basico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD26C3DD-4E75-48E9-BC7E-91689E48033A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF1F3D1B-44F3-47A3-AAC2-07BF272311C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20280" yWindow="-135" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{FB90DC12-CE7E-421E-A7F9-F06FD8601840}"/>
+    <workbookView showSheetTabs="0" xWindow="20280" yWindow="-135" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{FB90DC12-CE7E-421E-A7F9-F06FD8601840}"/>
   </bookViews>
   <sheets>
     <sheet name="Entrada e Saída" sheetId="1" r:id="rId1"/>
